--- a/medical_surveys_questionnaires/041_coronavirus_intake_form_for_massage_therapists--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/041_coronavirus_intake_form_for_massage_therapists--medical_surveys_questionnaires.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>true_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>True 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>false_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>False 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>none_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>self_quarantine</t>
+          <t>self_quarantine_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Self-Quarantine</t>
+          <t>Self Quarantine 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>isolation</t>
+          <t>isolation_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Isolation</t>
+          <t>Isolation 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
